--- a/tools/onboarding/mau/3-nhan-vien.xlsx
+++ b/tools/onboarding/mau/3-nhan-vien.xlsx
@@ -611,9 +611,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="33" t="inlineStr">
         <is>
@@ -682,7 +680,7 @@
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>Mỗi dòng Nhân viên có Email sẽ tạo tài khoản đăng nhập bằng email đó, mật khẩu ban đầu Bosskin@123, bắt đổi ở lần đăng nhập đầu. Phát tài khoản ngay sau khi nhập để không ai đăng nhập thay.</t>
+          <t>Mỗi dòng Nhân viên có Email sẽ tạo tài khoản đăng nhập bằng email đó với mật khẩu ngẫu nhiên. Nhập xong: Phân quyền → Người dùng → Xuất mật khẩu tạm để lấy file mật khẩu phát cho từng người; mỗi người phải đổi mật khẩu ở lần đăng nhập đầu.</t>
         </is>
       </c>
     </row>
